--- a/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T18:58:49+00:00</t>
+    <t>2024-03-12T11:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:AuditEventNorwayCommonTrustFramework/StructureDefinition/AuditEventEncounterExtension</t>
+    <t>urn:no-basis-auditevent/StructureDefinition/AuditEventEncounterExtension</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T11:58:51+00:00</t>
+    <t>2024-03-15T06:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,7 +322,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(urn:AuditEventNorwayCommonTrustFramework/StructureDefinition/AuditEventNorwayEncounter)
+    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/no-basis-encounter)
 </t>
   </si>
   <si>
@@ -648,7 +648,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="100.859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="70.078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.2</t>
+    <t>0.8.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T06:42:57+00:00</t>
+    <t>2024-03-15T09:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,7 +322,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/no-basis-encounter)
+    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/no-basis-encounter-auditevent)
 </t>
   </si>
   <si>
@@ -648,7 +648,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.63671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.3</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T09:00:42+00:00</t>
+    <t>2024-03-17T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -66,7 +66,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>

--- a/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventEncounterExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-06T16:49:55+00:00</t>
+    <t>2024-04-28T16:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,7 +322,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/no-basis-encounter-auditevent)
+    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/auditevent-encounter)
 </t>
   </si>
   <si>
@@ -648,7 +648,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.32421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
